--- a/scraper/failure_log.xlsx
+++ b/scraper/failure_log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,31 +441,6 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>Last Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Worldbeat Center</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NoEventsFound</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>scraper returned 0 events</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-09-04 07:46</t>
         </is>
       </c>
     </row>

--- a/scraper/failure_log.xlsx
+++ b/scraper/failure_log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,6 +441,31 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>Last Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Brick By Brick</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NoEventsFound</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>scraper returned 0 events</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:01</t>
         </is>
       </c>
     </row>

--- a/scraper/failure_log.xlsx
+++ b/scraper/failure_log.xlsx
@@ -461,11 +461,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:01</t>
+          <t>2026-09-28 14:41</t>
         </is>
       </c>
     </row>

--- a/scraper/failure_log.xlsx
+++ b/scraper/failure_log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,11 +461,136 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:41</t>
+          <t>2026-10-14 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Casbah</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HTTP 403</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.casbahmusic.com/</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-14 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Del Mar Fairgrounds</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NoEventsFound</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>scraper returned 0 events</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-14 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lou Lou's Jungle Room</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HTTP 403</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.casbahmusic.com/venues/lou-lous/</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-10-14 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Museum of Making Music</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NoEventsFound</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>scraper returned 0 events</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-14 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Quartyard</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HTTP 403</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://www.casbahmusic.com/</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-14 20:58</t>
         </is>
       </c>
     </row>
@@ -480,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,6 +635,31 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Brick By Brick</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NoEventsFound</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>scraper returned 0 events</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-10-14 20:58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
